--- a/excel/output_stats_vfvv/gemver/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/gemver/EfficiencyStats.xlsx
@@ -499,16 +499,16 @@
         <v>42.4896</v>
       </c>
       <c r="F2" t="n">
-        <v>354.08</v>
+        <v>356.41</v>
       </c>
       <c r="G2" t="n">
-        <v>355.79</v>
+        <v>358.51</v>
       </c>
       <c r="H2" t="n">
-        <v>351.286</v>
+        <v>352.135</v>
       </c>
       <c r="I2" t="n">
-        <v>351.432</v>
+        <v>352.392</v>
       </c>
       <c r="J2" t="n">
         <v>226227000</v>
